--- a/valora-demo/modelos/cementos-pacasmayo-modelo.xlsx
+++ b/valora-demo/modelos/cementos-pacasmayo-modelo.xlsx
@@ -6008,11 +6008,11 @@
         </is>
       </c>
       <c r="C28" s="29" t="n">
-        <v>0.06348424340539646</v>
+        <v>0.0614</v>
       </c>
       <c r="D28" s="27" t="inlineStr">
         <is>
-          <t>Default: |gastos financieros| / deuda financiera promedio (histórico)</t>
+          <t>Kd real ponderado por instrumento en PEN (deuda_financiera SMV, 100% saldo, 11/20 instrumentos) — ver kd_real.py</t>
         </is>
       </c>
     </row>
@@ -6133,12 +6133,12 @@
         </is>
       </c>
       <c r="C36" s="12">
-        <f>Supuestos!$C$43*Supuestos!$C$49</f>
+        <f>Supuestos!$C$35</f>
         <v/>
       </c>
       <c r="D36" s="27" t="inlineStr">
         <is>
-          <t>Market cap: precio convertido × acciones equivalentes</t>
+          <t>Sin precio de mercado: fallback al patrimonio contable</t>
         </is>
       </c>
     </row>
@@ -6204,12 +6204,10 @@
           <t>Precio acción común (moneda de cotización)</t>
         </is>
       </c>
-      <c r="C42" s="30" t="n">
-        <v>8.1</v>
-      </c>
+      <c r="C42" s="30" t="n"/>
       <c r="D42" s="27" t="inlineStr">
         <is>
-          <t>Cierre BVL (CPACASC1); editable</t>
+          <t>Sin dato automático (red/BVL); ingresar manualmente</t>
         </is>
       </c>
     </row>
@@ -6219,10 +6217,7 @@
           <t>Precio acción común en Soles (EEFF)</t>
         </is>
       </c>
-      <c r="C43" s="32">
-        <f>Supuestos!$C$42</f>
-        <v/>
-      </c>
+      <c r="C43" s="32" t="n"/>
       <c r="D43" s="27" t="inlineStr">
         <is>
           <t>Convertido con el tipo de cambio si la cotización es en otra moneda</t>
@@ -6236,11 +6231,11 @@
         </is>
       </c>
       <c r="C44" s="33" t="n">
-        <v>423868.449</v>
+        <v>428347.2222222222</v>
       </c>
       <c r="D44" s="27" t="inlineStr">
         <is>
-          <t>Default: BVL listStock (CPACASC1); editable</t>
+          <t>Default: Utilidad neta / EPS básica 2025; editable</t>
         </is>
       </c>
     </row>
@@ -6251,7 +6246,7 @@
         </is>
       </c>
       <c r="C45" s="33" t="n">
-        <v>40278.894</v>
+        <v>40279</v>
       </c>
       <c r="D45" s="27" t="inlineStr">
         <is>
@@ -6266,7 +6261,7 @@
         </is>
       </c>
       <c r="C46" s="33" t="n">
-        <v>121258</v>
+        <v>0</v>
       </c>
       <c r="D46" s="27" t="inlineStr">
         <is>
@@ -6280,12 +6275,10 @@
           <t>Precio acción de inversión</t>
         </is>
       </c>
-      <c r="C47" s="30" t="n">
-        <v>7</v>
-      </c>
+      <c r="C47" s="30" t="n"/>
       <c r="D47" s="27" t="inlineStr">
         <is>
-          <t>Cierre BVL (CPACASI1); editable</t>
+          <t>Sin dato automático; ingresar manualmente (si no aplica, dejar en 0)</t>
         </is>
       </c>
     </row>
@@ -6295,9 +6288,8 @@
           <t>Factor conversión inversión → común</t>
         </is>
       </c>
-      <c r="C48" s="32">
-        <f>Supuestos!$C$47/Supuestos!$C$42</f>
-        <v/>
+      <c r="C48" s="32" t="n">
+        <v>1</v>
       </c>
       <c r="D48" s="27" t="inlineStr">
         <is>
